--- a/laporan_padel_dki_jakarta_2026-09-21.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-21.xlsx
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.220.000</t>
+          <t>Rp3.930.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.450.000</t>
+          <t>Rp18.000.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp1.830.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.820.000</t>
+          <t>Rp10.380.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.150.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.046.000</t>
+          <t>Rp1.380.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-21.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-21.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp648.000</t>
+          <t>Rp846.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.240.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>96</v>
       </c>
       <c r="D83" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.190.000</t>
+          <t>Rp4.325.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp496.000</t>
+          <t>Rp602.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D61" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.025.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.321.000</t>
+          <t>Rp7.461.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>75</v>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp570.000</t>
+          <t>Rp1.438.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>36</v>
       </c>
       <c r="D46" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp4.380.000</t>
+          <t>Rp4.880.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7940,16 +7940,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.120.000</t>
+          <t>Rp4.720.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.775.000</t>
+          <t>Rp5.305.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.330.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-21.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-21.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp846.000</t>
+          <t>Rp622.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp795.000</t>
+          <t>Rp1.191.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp4.655.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp5.625.000</t>
+          <t>Rp6.125.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.445.000</t>
+          <t>Rp2.543.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.410.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>32</v>
       </c>
       <c r="D37" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp210.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp1.520.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp675.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>90</v>
       </c>
       <c r="D60" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp6.740.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>68</v>
       </c>
       <c r="D61" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp630.000</t>
+          <t>Rp970.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>176</v>
       </c>
       <c r="D68" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp598.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>102</v>
       </c>
       <c r="D69" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.962.500</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>80</v>
       </c>
       <c r="D78" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>96</v>
       </c>
       <c r="D83" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>36</v>
       </c>
       <c r="D91" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp1.021.000</t>
+          <t>Rp1.139.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>64</v>
       </c>
       <c r="D93" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp220.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp1.830.000</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp162.000</t>
+          <t>Rp324.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.472.003</t>
+          <t>Rp11.822.003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.645.000</t>
+          <t>Rp1.944.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>90</v>
       </c>
       <c r="D34" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.625.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp1.584.000</t>
+          <t>Rp2.376.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp602.000</t>
+          <t>Rp655.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.245.000</t>
+          <t>Rp14.685.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp31.950.000</t>
+          <t>Rp33.100.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.835.000</t>
+          <t>Rp8.510.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.580.000</t>
+          <t>Rp2.970.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.120.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.325.000</t>
+          <t>Rp6.025.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.744.000</t>
+          <t>Rp6.994.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp11.825.000</t>
+          <t>Rp12.105.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.513.000</t>
+          <t>Rp1.682.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.800.000</t>
+          <t>Rp22.600.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.345.000</t>
+          <t>Rp2.915.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp8.650.000</t>
+          <t>Rp9.090.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.425.000</t>
+          <t>Rp6.725.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.492.000</t>
+          <t>Rp4.244.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.438.000</t>
+          <t>Rp2.008.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp19.425.000</t>
+          <t>Rp19.875.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp8.850.000</t>
+          <t>Rp9.200.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.845.000</t>
+          <t>Rp8.375.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp23.200.000</t>
+          <t>Rp25.200.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp410.000</t>
+          <t>Rp860.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7940,16 +7940,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.720.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp520.000</t>
+          <t>Rp1.040.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.388.000</t>
+          <t>Rp3.687.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.085.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.290.000</t>
+          <t>Rp7.590.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.305.000</t>
+          <t>Rp3.905.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp3.645.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.390.000</t>
+          <t>Rp20.150.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.030.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.438.000</t>
+          <t>Rp1.736.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-21.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-21.xlsx
@@ -544,16 +544,16 @@
         <v>184</v>
       </c>
       <c r="D4" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.089.990</t>
+          <t>Rp4.989.990</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp6.625.000</t>
+          <t>Rp3.875.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp7.908.500</t>
+          <t>Rp8.376.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.770.000</t>
+          <t>Rp3.245.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>15</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp747.000</t>
+          <t>Rp1.245.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.170.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp210.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>60</v>
       </c>
       <c r="D43" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.699.000</t>
+          <t>Rp2.499.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>42</v>
       </c>
       <c r="D44" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>96</v>
       </c>
       <c r="D46" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.119.000</t>
+          <t>Rp2.015.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>64</v>
       </c>
       <c r="D50" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.168.000</t>
+          <t>Rp3.456.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.520.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>54</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp815.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp298.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>90</v>
       </c>
       <c r="D60" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp6.740.000</t>
+          <t>Rp7.360.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>68</v>
       </c>
       <c r="D61" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp970.000</t>
+          <t>Rp2.510.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>34</v>
       </c>
       <c r="D63" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp180.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp7.078.000</t>
+          <t>Rp8.674.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>34</v>
       </c>
       <c r="D67" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>102</v>
       </c>
       <c r="D69" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.525.000</t>
+          <t>Rp2.087.500</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>96</v>
       </c>
       <c r="D73" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp4.970.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>120</v>
       </c>
       <c r="D75" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.520.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp3.125.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,21 +2838,21 @@
         <v>80</v>
       </c>
       <c r="D78" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.260.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp125.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2962,16 +2962,16 @@
         <v>135</v>
       </c>
       <c r="D82" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.760.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>138</v>
       </c>
       <c r="D86" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp5.925.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="D87" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp3.630.000</t>
+          <t>Rp4.170.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>36</v>
       </c>
       <c r="D89" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp430.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>28</v>
       </c>
       <c r="D90" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp2.310.000</t>
+          <t>Rp2.710.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp324.000</t>
+          <t>Rp567.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.822.003</t>
+          <t>Rp12.347.003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.750.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp798.000</t>
+          <t>Rp1.323.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp10.000.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.035.000</t>
+          <t>Rp6.010.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.375.000</t>
+          <t>Rp5.775.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp99.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.486.000</t>
+          <t>Rp3.984.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>159</v>
       </c>
       <c r="D38" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp12.500.000</t>
+          <t>Rp13.050.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.599.000</t>
+          <t>Rp3.499.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp2.376.000</t>
+          <t>Rp3.168.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>38</v>
       </c>
       <c r="D57" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp3.975.000</t>
+          <t>Rp4.635.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>144</v>
       </c>
       <c r="D58" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp655.000</t>
+          <t>Rp708.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>51</v>
       </c>
       <c r="D60" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp280.000</t>
+          <t>Rp840.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.415.000</t>
+          <t>Rp2.695.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>92</v>
       </c>
       <c r="D68" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp9.040.000</t>
+          <t>Rp9.390.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp7.750.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.685.000</t>
+          <t>Rp18.755.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp690.000</t>
+          <t>Rp590.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.970.000</t>
+          <t>Rp3.270.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.340.000</t>
+          <t>Rp2.910.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.420.000</t>
+          <t>Rp11.280.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.380.000</t>
+          <t>Rp10.830.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp10.420.000</t>
+          <t>Rp10.615.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.025.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.994.000</t>
+          <t>Rp7.466.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp12.105.000</t>
+          <t>Rp13.505.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.076.000</t>
+          <t>Rp4.251.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp198.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.600.000</t>
+          <t>Rp23.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp6.775.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.461.000</t>
+          <t>Rp6.265.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.915.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp9.090.000</t>
+          <t>Rp9.580.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.725.000</t>
+          <t>Rp7.025.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>34</v>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.180.000</t>
+          <t>Rp3.332.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp9.200.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.420.000</t>
+          <t>Rp5.220.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>48</v>
       </c>
       <c r="D50" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.415.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7940,16 +7940,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.820.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.590.000</t>
+          <t>Rp7.080.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.905.000</t>
+          <t>Rp5.040.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.026.000</t>
+          <t>Rp5.196.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.150.000</t>
+          <t>Rp21.710.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp398.000</t>
+          <t>Rp597.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp270.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.380.000</t>
+          <t>Rp2.370.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp770.000</t>
+          <t>Rp2.370.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp685.000</t>
+          <t>Rp1.075.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.058.000</t>
+          <t>Rp2.588.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.736.000</t>
+          <t>Rp1.934.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp169.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.725.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-21.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-21.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp560.000</t>
+          <t>Rp640.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.989.990</t>
+          <t>Rp4.789.990</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.376.000</t>
+          <t>Rp8.876.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.930.000</t>
+          <t>Rp4.130.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.290.000</t>
+          <t>Rp5.540.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp694.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>68</v>
       </c>
       <c r="D61" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.510.000</t>
+          <t>Rp2.770.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp675.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>80</v>
       </c>
       <c r="D78" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.260.000</t>
+          <t>Rp2.635.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>138</v>
       </c>
       <c r="D86" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.925.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.347.003</t>
+          <t>Rp12.632.003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp10.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.775.000</t>
+          <t>Rp5.575.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp9.315.000</t>
+          <t>Rp9.490.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>54</v>
       </c>
       <c r="D42" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>38</v>
       </c>
       <c r="D57" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp4.635.000</t>
+          <t>Rp4.910.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.755.000</t>
+          <t>Rp19.910.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp397.000</t>
+          <t>Rp772.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.725.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.265.000</t>
+          <t>Rp6.465.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.325.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp7.025.000</t>
+          <t>Rp7.325.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp19.875.000</t>
+          <t>Rp20.075.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp860.000</t>
+          <t>Rp1.310.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.330.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.075.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.650.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
